--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.aguilar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DEA63B7-C084-4AF2-914F-117754E3A42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35051CCF-792F-4CB6-AFDF-A7F10AC2F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Usuario</t>
   </si>
@@ -94,6 +94,12 @@
   </si>
   <si>
     <t>Pablo Madrueño</t>
+  </si>
+  <si>
+    <t>Megan Nelson</t>
+  </si>
+  <si>
+    <t>David Barbero</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -517,6 +523,28 @@
         <v>1234</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>1234</v>
+      </c>
+      <c r="C8">
+        <v>150.15100000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>1234</v>
+      </c>
+      <c r="C9">
+        <v>257</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>

--- a/usuarios.xlsx
+++ b/usuarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.aguilar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35051CCF-792F-4CB6-AFDF-A7F10AC2F289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC6822-7D36-47FD-AEA0-67CE0105CDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>Usuario</t>
   </si>
@@ -100,6 +100,42 @@
   </si>
   <si>
     <t>David Barbero</t>
+  </si>
+  <si>
+    <t>Floren</t>
+  </si>
+  <si>
+    <t>Meridastone</t>
+  </si>
+  <si>
+    <t>Rafael Aís Azor</t>
+  </si>
+  <si>
+    <t>Mármoles Azor</t>
+  </si>
+  <si>
+    <t>Javier Jiménez</t>
+  </si>
+  <si>
+    <t>Rafael Alastur</t>
+  </si>
+  <si>
+    <t>Alastur</t>
+  </si>
+  <si>
+    <t>Jose Mesa</t>
+  </si>
+  <si>
+    <t>Jose Quevedo</t>
+  </si>
+  <si>
+    <t>Tello</t>
+  </si>
+  <si>
+    <t>Teidemar</t>
+  </si>
+  <si>
+    <t>Canarycells</t>
   </si>
 </sst>
 </file>
@@ -119,6 +155,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -452,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -545,6 +582,80 @@
         <v>257</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>1234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>1234</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>1234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>1234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>1234</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>1234</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
